--- a/AAII_Financials/Quarterly/BAM_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BAM_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="92">
   <si>
     <t>BAM</t>
   </si>
@@ -656,205 +656,209 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="42" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="43" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2" t="s">
-        <v>8</v>
-      </c>
       <c r="R7" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="S7" s="2">
+      <c r="S7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="X7" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y7" s="2">
+      <c r="Y7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1753000</v>
+      </c>
+      <c r="E8" s="3">
         <v>1338000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1394000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1252000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1090000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1081000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1063000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1117000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>916000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>884000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1130000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>893000</v>
       </c>
-      <c r="O8" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P8" s="3" t="s">
         <v>8</v>
       </c>
@@ -864,125 +868,128 @@
       <c r="R8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S8" s="3">
+      <c r="S8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T8" s="3">
         <v>924000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>755000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>3087000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>741000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>632000</v>
       </c>
-      <c r="X8" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y8" s="3">
+      <c r="Y8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z8" s="3">
         <v>17088000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>16249000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>12829000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>16586000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>17819000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>17875000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>16924000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>15208000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>16006000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>14858000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>13276000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>12631000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>13065000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>12276000</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>9444000</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>6001000</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>6935000</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>6285000</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>405000</v>
+      </c>
+      <c r="E9" s="3">
         <v>355000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>331000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>379000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>404000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>259000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>276000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>326000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>277000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>275000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>283000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>208000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>37000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>84000</v>
       </c>
-      <c r="Q9" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R9" s="3" t="s">
         <v>8</v>
       </c>
@@ -1004,107 +1011,110 @@
       <c r="X9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Y9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z9" s="3">
         <v>12859000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>12372000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>9446000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>12709000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>13848000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>13910000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>13385000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>11585000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>12680000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>11967000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>10781000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>10091000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>10635000</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>10034000</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>7332000</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>4387000</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>5150000</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>4590000</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1348000</v>
+      </c>
+      <c r="E10" s="3">
         <v>983000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1063000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>873000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>686000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>822000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>787000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>791000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>639000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>609000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>847000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>685000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>-37000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>-84000</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R10" s="3" t="s">
         <v>8</v>
       </c>
@@ -1126,62 +1136,65 @@
       <c r="X10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Y10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z10" s="3">
         <v>4229000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>3877000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>3383000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>3877000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>3971000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>3965000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>3539000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>3623000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>3326000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>2891000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>2495000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>2540000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>2430000</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>2242000</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>2112000</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>1614000</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>1785000</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>1695000</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1224,8 +1237,9 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1346,8 +1360,11 @@
       <c r="AP12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1468,52 +1485,55 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-62000</v>
+      </c>
+      <c r="E14" s="3">
         <v>8000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>3000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>64000</v>
-      </c>
-      <c r="G14" s="3">
-        <v>-13000</v>
       </c>
       <c r="H14" s="3">
         <v>26000</v>
       </c>
       <c r="I14" s="3">
+        <v>26000</v>
+      </c>
+      <c r="J14" s="3">
         <v>39000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>41000</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M14" s="3">
         <v>72000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>139000</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O14" s="3" t="s">
         <v>8</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
@@ -1590,8 +1610,11 @@
       <c r="AP14" s="3">
         <v>0</v>
       </c>
+      <c r="AQ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1599,44 +1622,44 @@
         <v>13000</v>
       </c>
       <c r="E15" s="3">
+        <v>13000</v>
+      </c>
+      <c r="F15" s="3">
         <v>10000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>16000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>11000</v>
-      </c>
-      <c r="H15" s="3">
-        <v>3000</v>
       </c>
       <c r="I15" s="3">
         <v>3000</v>
       </c>
       <c r="J15" s="3">
+        <v>3000</v>
+      </c>
+      <c r="K15" s="3">
         <v>4000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>3000</v>
-      </c>
-      <c r="L15" s="3">
-        <v>4000</v>
       </c>
       <c r="M15" s="3">
         <v>4000</v>
       </c>
       <c r="N15" s="3">
+        <v>4000</v>
+      </c>
+      <c r="O15" s="3">
         <v>3000</v>
       </c>
-      <c r="O15" s="3">
-        <v>0</v>
-      </c>
       <c r="P15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="3">
         <v>3300</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
@@ -1659,61 +1682,64 @@
         <v>0</v>
       </c>
       <c r="Y15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z15" s="3">
         <v>1536000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>1470000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>1376000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>1409000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>1309000</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>1299000</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>1234000</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>1034000</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>927000</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>833000</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>672000</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>670000</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>590000</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>643000</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>613000</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>499000</v>
       </c>
-      <c r="AO15" s="3">
+      <c r="AP15" s="3">
         <v>482000</v>
       </c>
-      <c r="AP15" s="3">
+      <c r="AQ15" s="3">
         <v>541000</v>
       </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1753,252 +1779,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>548000</v>
+      </c>
+      <c r="E17" s="3">
         <v>475000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>447000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>489000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>504000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>343000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>407000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>430000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>368000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>360000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>415000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>307000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>-10000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>-53000</v>
       </c>
-      <c r="Q17" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R17" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S17" s="3">
+      <c r="S17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T17" s="3">
         <v>284000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>415000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1402000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>356000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>353000</v>
       </c>
-      <c r="X17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y17" s="3">
+      <c r="Y17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z17" s="3">
         <v>15030000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>15482000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>14317000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>16379000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>15981000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>16299000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>15981000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>13716000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>13862000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>13773000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>11273000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>10623000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>10872000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>11025000</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>8367000</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>5358000</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>6627000</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>5256000</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>1205000</v>
+      </c>
+      <c r="E18" s="3">
         <v>863000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>947000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>763000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>586000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>738000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>656000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>687000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>548000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>524000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>715000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>586000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>10000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>53000</v>
       </c>
-      <c r="Q18" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R18" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S18" s="3">
+      <c r="S18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T18" s="3">
         <v>640000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>340000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>1685000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>385000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>279000</v>
       </c>
-      <c r="X18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y18" s="3">
+      <c r="Y18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z18" s="3">
         <v>2058000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>767000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-1488000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>207000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>1838000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>1576000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>943000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>1492000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>2144000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>1085000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>2003000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>2008000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>2193000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>1251000</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>1077000</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>643000</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>308000</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>1029000</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2041,76 +2074,77 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-178000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-99000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-22000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-123000</v>
       </c>
-      <c r="G20" s="3">
-        <v>-114000</v>
-      </c>
       <c r="H20" s="3">
+        <v>-153000</v>
+      </c>
+      <c r="I20" s="3">
         <v>-29000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-208000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-33000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-141000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-80000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-73000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>18000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-115000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-129000</v>
       </c>
-      <c r="Q20" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S20" s="3">
+      <c r="S20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T20" s="3">
         <v>356000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>525000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>1665000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>209000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>375000</v>
       </c>
-      <c r="X20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y20" s="3">
-        <v>0</v>
+      <c r="Y20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Z20" s="3">
         <v>0</v>
@@ -2163,180 +2197,186 @@
       <c r="AP20" s="3">
         <v>0</v>
       </c>
+      <c r="AQ20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1396000</v>
+      </c>
+      <c r="E21" s="3">
         <v>975000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>979000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>902000</v>
       </c>
-      <c r="G21" s="3">
-        <v>711000</v>
-      </c>
       <c r="H21" s="3">
+        <v>750000</v>
+      </c>
+      <c r="I21" s="3">
         <v>770000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>867000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>724000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>692000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>608000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>792000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>571000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>125000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>185300</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S21" s="3">
+      <c r="S21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T21" s="3">
         <v>998000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>868000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>3361000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>596000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>656000</v>
       </c>
-      <c r="X21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y21" s="3">
+      <c r="Y21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z21" s="3">
         <v>3594000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>2237000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-112000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1616000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>3147000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>2875000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>2177000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>2526000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>3071000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1918000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>2675000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>2678000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>2783000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>1894000</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>1690000</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>1142000</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>790000</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>1570000</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>111000</v>
+      </c>
+      <c r="E22" s="3">
         <v>258000</v>
-      </c>
-      <c r="E22" s="3">
-        <v>52000</v>
       </c>
       <c r="F22" s="3">
         <v>52000</v>
       </c>
       <c r="G22" s="3">
+        <v>52000</v>
+      </c>
+      <c r="H22" s="3">
         <v>54000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>159000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>16000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>46000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>29000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>88000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>2000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>6000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>16000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>57000</v>
       </c>
-      <c r="Q22" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S22" s="3">
-        <v>0</v>
+      <c r="S22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="T22" s="3">
         <v>0</v>
@@ -2407,252 +2447,261 @@
       <c r="AP22" s="3">
         <v>0</v>
       </c>
+      <c r="AQ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1334000</v>
+      </c>
+      <c r="E23" s="3">
         <v>696000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>914000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>770000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>659000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>582000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>809000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>633000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>660000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>444000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>647000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>562000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>109000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>125000</v>
       </c>
-      <c r="Q23" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R23" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S23" s="3">
+      <c r="S23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T23" s="3">
         <v>996000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>865000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>3350000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>594000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>654000</v>
       </c>
-      <c r="X23" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y23" s="3">
+      <c r="Y23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z23" s="3">
         <v>2058000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>767000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-1488000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>207000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>1838000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1576000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>943000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>1492000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>2144000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>1085000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>2003000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>2008000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>2193000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>1251000</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>1077000</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>643000</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>308000</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>1029000</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>162000</v>
+      </c>
+      <c r="E24" s="3">
         <v>110000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>299000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>78000</v>
-      </c>
-      <c r="G24" s="3">
-        <v>75000</v>
       </c>
       <c r="H24" s="3">
         <v>75000</v>
       </c>
       <c r="I24" s="3">
+        <v>75000</v>
+      </c>
+      <c r="J24" s="3">
         <v>129000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>96000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>142000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>71000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>116000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>52000</v>
       </c>
-      <c r="O24" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q24" s="3">
-        <v>0</v>
+      <c r="Q24" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R24" s="3">
         <v>0</v>
       </c>
       <c r="S24" s="3">
+        <v>0</v>
+      </c>
+      <c r="T24" s="3">
         <v>162000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>142000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>504000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>62000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>89000</v>
       </c>
-      <c r="X24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y24" s="3">
+      <c r="Y24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z24" s="3">
         <v>243000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>225000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>5000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>364000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>200000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-180000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>239000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>236000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>-884000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>144000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>339000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>153000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>110000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>259000</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>119000</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>125000</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>211000</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>-992000</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2773,252 +2822,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1172000</v>
+      </c>
+      <c r="E26" s="3">
         <v>586000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>615000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>692000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>584000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>507000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>680000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>537000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>518000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>373000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>531000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>510000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>109000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>125000</v>
       </c>
-      <c r="Q26" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R26" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S26" s="3">
+      <c r="S26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T26" s="3">
         <v>834000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>723000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>2846000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>532000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>565000</v>
       </c>
-      <c r="X26" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y26" s="3">
+      <c r="Y26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z26" s="3">
         <v>1815000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>542000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-1493000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-157000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>1638000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>1756000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>704000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>1256000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>3028000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>941000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>1664000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>1855000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>2083000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>992000</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>958000</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>518000</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>97000</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>2021000</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>904000</v>
+      </c>
+      <c r="E27" s="3">
         <v>617000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>560000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>724000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>620000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>581000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>688000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>544000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>495000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>441000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>374000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>494000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>109000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>125000</v>
       </c>
-      <c r="Q27" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R27" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S27" s="3">
+      <c r="S27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T27" s="3">
         <v>668000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>348000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>1869000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>414000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>427000</v>
       </c>
-      <c r="X27" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y27" s="3">
+      <c r="Y27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z27" s="3">
         <v>607000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>138000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-692000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-328000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>807000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>909000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>361000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>578000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>1847000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>125000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>642000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>819000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>1007000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>193000</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>190000</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>-73000</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>140000</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>1003000</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3139,8 +3197,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3261,8 +3322,11 @@
       <c r="AP29" s="3">
         <v>0</v>
       </c>
+      <c r="AQ29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3383,8 +3447,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3505,76 +3572,79 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>178000</v>
+      </c>
+      <c r="E32" s="3">
         <v>99000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>22000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>123000</v>
       </c>
-      <c r="G32" s="3">
-        <v>114000</v>
-      </c>
       <c r="H32" s="3">
+        <v>153000</v>
+      </c>
+      <c r="I32" s="3">
         <v>29000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>208000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>33000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>141000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>80000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>73000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-18000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>115000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>129000</v>
       </c>
-      <c r="Q32" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S32" s="3">
+      <c r="S32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T32" s="3">
         <v>-356000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-525000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-1665000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-209000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-375000</v>
       </c>
-      <c r="X32" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y32" s="3">
-        <v>0</v>
+      <c r="Y32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Z32" s="3">
         <v>0</v>
@@ -3627,130 +3697,136 @@
       <c r="AP32" s="3">
         <v>0</v>
       </c>
+      <c r="AQ32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>904000</v>
+      </c>
+      <c r="E33" s="3">
         <v>617000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>560000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>724000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>620000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>581000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>688000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>544000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>495000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>441000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>374000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>494000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>109000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>125000</v>
       </c>
-      <c r="Q33" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R33" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S33" s="3">
+      <c r="S33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T33" s="3">
         <v>668000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>348000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>1869000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>414000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>427000</v>
       </c>
-      <c r="X33" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y33" s="3">
+      <c r="Y33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z33" s="3">
         <v>607000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>138000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-692000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-328000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>807000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>909000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>361000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>578000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>1847000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>125000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>642000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>819000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>1007000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>193000</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>190000</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>-73000</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>140000</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>1003000</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3871,257 +3947,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>904000</v>
+      </c>
+      <c r="E35" s="3">
         <v>617000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>560000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>724000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>620000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>581000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>688000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>544000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>495000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>441000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>374000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>494000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>109000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>125000</v>
       </c>
-      <c r="Q35" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R35" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S35" s="3">
+      <c r="S35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T35" s="3">
         <v>668000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>348000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>1869000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>414000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>427000</v>
       </c>
-      <c r="X35" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y35" s="3">
+      <c r="Y35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z35" s="3">
         <v>607000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>138000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-692000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-328000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>807000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>909000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>361000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>578000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>1847000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>125000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>642000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>819000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>1007000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>193000</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>190000</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>-73000</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>140000</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>1003000</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2" t="s">
-        <v>8</v>
-      </c>
       <c r="R38" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="S38" s="2">
+      <c r="S38" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="X38" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y38" s="2">
+      <c r="Y38" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4164,8 +4249,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4208,62 +4294,63 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1503000</v>
+      </c>
+      <c r="E41" s="3">
         <v>1096000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1583000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1062000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>480000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>332000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>404000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>903000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1931000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2594000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2667000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2945000</v>
-      </c>
-      <c r="O41" s="3">
-        <v>12000</v>
       </c>
       <c r="P41" s="3">
         <v>12000</v>
       </c>
-      <c r="Q41" s="3" t="s">
-        <v>8</v>
+      <c r="Q41" s="3">
+        <v>12000</v>
       </c>
       <c r="R41" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S41" s="3">
+      <c r="S41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T41" s="3">
         <v>2640000</v>
       </c>
-      <c r="T41" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U41" s="3" t="s">
         <v>8</v>
       </c>
@@ -4276,62 +4363,65 @@
       <c r="X41" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Y41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z41" s="3">
         <v>9933000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>8723000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>9523000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>9868000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>6778000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>7595000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>7447000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>6740000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>8390000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>7839000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>5913000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>6044000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>5139000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>4538000</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>4429000</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>6427000</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>4299000</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>4372000</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4452,62 +4542,65 @@
       <c r="AP42" s="3">
         <v>0</v>
       </c>
+      <c r="AQ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>2939000</v>
+        <v>3537000</v>
       </c>
       <c r="E43" s="3">
+        <v>3379000</v>
+      </c>
+      <c r="F43" s="3">
         <v>3386000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>3781000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>3918000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>3832000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2725000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2992000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2875000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2926000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2931000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2600000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>810000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>875000</v>
       </c>
-      <c r="Q43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S43" s="3">
+      <c r="S43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T43" s="3">
         <v>1063000</v>
       </c>
-      <c r="T43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U43" s="3" t="s">
         <v>8</v>
       </c>
@@ -4520,62 +4613,65 @@
       <c r="X43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Y43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z43" s="3">
         <v>18928000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>18268000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>17140000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>18381000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>18469000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>19080000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>17693000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>16554000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>16931000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>15424000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>12656000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>12257000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>11973000</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>11300000</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>11183000</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>9055000</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>8746000</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>8882000</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4618,8 +4714,8 @@
       <c r="P44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -4643,115 +4739,118 @@
         <v>0</v>
       </c>
       <c r="Y44" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z44" s="3">
         <v>10360000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>10374000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>10212000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>9719000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>10272000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>9732000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>9761000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>7219000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>6989000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>7312000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>6560000</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>6638000</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>6311000</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>6648000</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>6290000</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>5437000</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>5349000</v>
       </c>
-      <c r="AP44" s="3">
+      <c r="AQ44" s="3">
         <v>5869000</v>
       </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>504000</v>
+      </c>
+      <c r="E45" s="3">
         <v>433000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>410000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>265000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>290000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>209000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>231000</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L45" s="3">
         <v>45000</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N45" s="3">
         <v>37000</v>
       </c>
-      <c r="N45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O45" s="3" t="s">
         <v>8</v>
       </c>
       <c r="P45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q45" s="3">
-        <v>0</v>
+      <c r="Q45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R45" s="3">
         <v>0</v>
       </c>
       <c r="S45" s="3">
+        <v>0</v>
+      </c>
+      <c r="T45" s="3">
         <v>76000</v>
       </c>
-      <c r="T45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U45" s="3" t="s">
         <v>8</v>
       </c>
@@ -4764,8 +4863,8 @@
       <c r="X45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y45" s="3">
-        <v>0</v>
+      <c r="Y45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Z45" s="3">
         <v>0</v>
@@ -4818,53 +4917,56 @@
       <c r="AP45" s="3">
         <v>0</v>
       </c>
+      <c r="AQ45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>4468000</v>
+        <v>5544000</v>
       </c>
       <c r="E46" s="3">
+        <v>4908000</v>
+      </c>
+      <c r="F46" s="3">
         <v>5507000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>5108000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>4688000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>4373000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>3535000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>3895000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>4851000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>5520000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>5759000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>5545000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>822000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>887000</v>
       </c>
-      <c r="Q46" s="3">
-        <v>0</v>
-      </c>
       <c r="R46" s="3">
         <v>0</v>
       </c>
@@ -4940,62 +5042,65 @@
       <c r="AP46" s="3">
         <v>0</v>
       </c>
+      <c r="AQ46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>13452000</v>
+      </c>
+      <c r="E47" s="3">
         <v>11897000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>10307000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>10128000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>10231000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>9418000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>9606000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>9354000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>8276000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>7359000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>7522000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>7336000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>2346000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>2415000</v>
       </c>
-      <c r="Q47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S47" s="3">
+      <c r="S47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T47" s="3">
         <v>21188000</v>
       </c>
-      <c r="T47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U47" s="3" t="s">
         <v>8</v>
       </c>
@@ -5008,116 +5113,119 @@
       <c r="X47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Y47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z47" s="3">
         <v>59057000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>56908000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>53566000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>50953000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>53166000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>47983000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>42925000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>41377000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>39874000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>37567000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>35614000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>36021000</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>36794000</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>34015000</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>31291000</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>29629000</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>29677000</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>29549000</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>97000</v>
+      </c>
+      <c r="E48" s="3">
         <v>93000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>92000</v>
       </c>
-      <c r="F48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="G48" s="3" t="s">
         <v>8</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I48" s="3">
+      <c r="I48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J48" s="3">
         <v>58000</v>
       </c>
-      <c r="J48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K48" s="3" t="s">
         <v>8</v>
       </c>
       <c r="L48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M48" s="3">
+      <c r="M48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N48" s="3">
         <v>73000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>69000</v>
       </c>
-      <c r="O48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q48" s="3">
-        <v>0</v>
+      <c r="Q48" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R48" s="3">
         <v>0</v>
       </c>
       <c r="S48" s="3">
+        <v>0</v>
+      </c>
+      <c r="T48" s="3">
         <v>62000</v>
       </c>
-      <c r="T48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U48" s="3" t="s">
         <v>8</v>
       </c>
@@ -5130,74 +5238,77 @@
       <c r="X48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Y48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z48" s="3">
         <v>196791000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>186390000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>182954000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>180622000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>185950000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>163406000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>164022000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>157908000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>151603000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>138905000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>114135000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>112740000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>109875000</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>104053000</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>102861000</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>102745000</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>99518000</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>95577000</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>458000</v>
+      </c>
+      <c r="E49" s="3">
         <v>465000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>470000</v>
       </c>
-      <c r="F49" s="3">
-        <v>0</v>
-      </c>
       <c r="G49" s="3">
         <v>0</v>
       </c>
@@ -5205,11 +5316,11 @@
         <v>0</v>
       </c>
       <c r="I49" s="3">
+        <v>0</v>
+      </c>
+      <c r="J49" s="3">
         <v>289000</v>
       </c>
-      <c r="J49" s="3">
-        <v>0</v>
-      </c>
       <c r="K49" s="3">
         <v>0</v>
       </c>
@@ -5217,14 +5328,14 @@
         <v>0</v>
       </c>
       <c r="M49" s="3">
+        <v>0</v>
+      </c>
+      <c r="N49" s="3">
         <v>293000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>319000</v>
       </c>
-      <c r="O49" s="3">
-        <v>0</v>
-      </c>
       <c r="P49" s="3">
         <v>0</v>
       </c>
@@ -5235,11 +5346,11 @@
         <v>0</v>
       </c>
       <c r="S49" s="3">
+        <v>0</v>
+      </c>
+      <c r="T49" s="3">
         <v>308000</v>
       </c>
-      <c r="T49" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U49" s="3" t="s">
         <v>8</v>
       </c>
@@ -5252,62 +5363,65 @@
       <c r="X49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Y49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z49" s="3">
         <v>39372000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>39117000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>38933000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>38489000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>42260000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>36193000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>37312000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>27649000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>27577000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>23158000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>19699000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>19747000</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>19559000</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>19938000</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>19151000</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>10177000</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>9856000</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>10226000</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5428,8 +5542,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5550,41 +5667,44 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
-        <v>440000</v>
-      </c>
-      <c r="E52" s="3">
+      <c r="D52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F52" s="3">
         <v>99000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>583000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>577000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>562000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>83000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>352000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>363000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>366000</v>
       </c>
-      <c r="M52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N52" s="3" t="s">
         <v>8</v>
       </c>
@@ -5594,18 +5714,18 @@
       <c r="P52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q52" s="3">
-        <v>0</v>
+      <c r="Q52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R52" s="3">
         <v>0</v>
       </c>
       <c r="S52" s="3">
+        <v>0</v>
+      </c>
+      <c r="T52" s="3">
         <v>2182000</v>
       </c>
-      <c r="T52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U52" s="3" t="s">
         <v>8</v>
       </c>
@@ -5618,62 +5738,65 @@
       <c r="X52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Y52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z52" s="3">
         <v>9255000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>7303000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>4107000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>4551000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>7074000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>7419000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>7176000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>6778000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>4917000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>3756000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>4591000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>2488000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>3069000</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>4085000</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>2978000</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>2526000</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>1994000</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>5362000</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5794,62 +5917,65 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>20080000</v>
+      </c>
+      <c r="E54" s="3">
         <v>17937000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>17047000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>16521000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>16143000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>14966000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>14157000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>14254000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>14147000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>13925000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>14290000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>14122000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>3168000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>3302000</v>
       </c>
-      <c r="Q54" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R54" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S54" s="3">
+      <c r="S54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T54" s="3">
         <v>27519000</v>
       </c>
-      <c r="T54" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U54" s="3" t="s">
         <v>8</v>
       </c>
@@ -5862,62 +5988,65 @@
       <c r="X54" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Y54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z54" s="3">
         <v>343696000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>327083000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>316435000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>312583000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>323969000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>291408000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>286336000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>264225000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>256281000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>233961000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>199168000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>195935000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>192720000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>184577000</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>178183000</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>165996000</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>159826000</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>159837000</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5960,8 +6089,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -6004,62 +6134,63 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2032000</v>
+      </c>
+      <c r="E57" s="3">
         <v>1953000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>599000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2495000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2357000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2118000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>490000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1667000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1906000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1697000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>537000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1768000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>766000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>873000</v>
       </c>
-      <c r="Q57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S57" s="3">
+      <c r="S57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T57" s="3">
         <v>570000</v>
       </c>
-      <c r="T57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U57" s="3" t="s">
         <v>8</v>
       </c>
@@ -6072,74 +6203,77 @@
       <c r="X57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Y57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z57" s="3">
         <v>50682000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>45153000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>42235000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>40504000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>43077000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>34174000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>32595000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>27928000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>23989000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>22546000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>18330000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>18656000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>17965000</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>17045000</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>15870000</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>12025000</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>11915000</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>12478000</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>463000</v>
+      </c>
+      <c r="E58" s="3">
         <v>451000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>462000</v>
       </c>
-      <c r="F58" s="3">
-        <v>0</v>
-      </c>
       <c r="G58" s="3">
         <v>0</v>
       </c>
@@ -6147,10 +6281,10 @@
         <v>0</v>
       </c>
       <c r="I58" s="3">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3">
         <v>251000</v>
-      </c>
-      <c r="J58" s="3">
-        <v>202000</v>
       </c>
       <c r="K58" s="3">
         <v>202000</v>
@@ -6159,29 +6293,29 @@
         <v>202000</v>
       </c>
       <c r="M58" s="3">
+        <v>202000</v>
+      </c>
+      <c r="N58" s="3">
         <v>198000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>194000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>124000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>95000</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S58" s="3">
+      <c r="S58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T58" s="3">
         <v>1315000</v>
       </c>
-      <c r="T58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U58" s="3" t="s">
         <v>8</v>
       </c>
@@ -6194,116 +6328,119 @@
       <c r="X58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Y58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z58" s="3">
         <v>21287000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>18819000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>19091000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>15015000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>15563000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>12457000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>11039000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>11327000</v>
       </c>
-      <c r="AG58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AH58" s="3">
+      <c r="AH58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI58" s="3">
         <v>9236000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>9401000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>9948000</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>10756000</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>7956000</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>8290000</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>8536000</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>8946000</v>
       </c>
-      <c r="AP58" s="3">
+      <c r="AQ58" s="3">
         <v>7873000</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>619000</v>
+      </c>
+      <c r="E59" s="3">
         <v>632000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>444000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>393000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>402000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>302000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>228000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>841000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>788000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>695000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>122000</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O59" s="3" t="s">
         <v>8</v>
       </c>
       <c r="P59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q59" s="3">
-        <v>0</v>
+      <c r="Q59" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R59" s="3">
         <v>0</v>
       </c>
       <c r="S59" s="3">
+        <v>0</v>
+      </c>
+      <c r="T59" s="3">
         <v>7263000</v>
       </c>
-      <c r="T59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U59" s="3" t="s">
         <v>8</v>
       </c>
@@ -6316,8 +6453,8 @@
       <c r="X59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y59" s="3">
-        <v>0</v>
+      <c r="Y59" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Z59" s="3">
         <v>0</v>
@@ -6370,53 +6507,56 @@
       <c r="AP59" s="3">
         <v>0</v>
       </c>
+      <c r="AQ59" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>4358000</v>
+      </c>
+      <c r="E60" s="3">
         <v>3968000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>3136000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>3787000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>3749000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>3337000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2663000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>3053000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2896000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2594000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2419000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2627000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>890000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>968000</v>
       </c>
-      <c r="Q60" s="3">
-        <v>0</v>
-      </c>
       <c r="R60" s="3">
         <v>0</v>
       </c>
@@ -6492,29 +6632,32 @@
       <c r="AP60" s="3">
         <v>0</v>
       </c>
+      <c r="AQ60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>3626000</v>
+      </c>
+      <c r="E61" s="3">
         <v>2512000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2478000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1939000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1250000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>639000</v>
       </c>
-      <c r="I61" s="3">
-        <v>0</v>
-      </c>
       <c r="J61" s="3">
         <v>0</v>
       </c>
@@ -6543,11 +6686,11 @@
         <v>0</v>
       </c>
       <c r="S61" s="3">
+        <v>0</v>
+      </c>
+      <c r="T61" s="3">
         <v>4084000</v>
       </c>
-      <c r="T61" s="3">
-        <v>0</v>
-      </c>
       <c r="U61" s="3">
         <v>0</v>
       </c>
@@ -6561,61 +6704,64 @@
         <v>0</v>
       </c>
       <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z61" s="3">
         <v>127114000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>129998000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>125322000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>125980000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>127812000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>117782000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>119392000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>107682000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>118218000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>97738000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>79662000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>74302000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>71294000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>69008000</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>67327000</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>65127000</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>59510000</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>60917000</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -6623,53 +6769,53 @@
         <v>14000</v>
       </c>
       <c r="E62" s="3">
+        <v>14000</v>
+      </c>
+      <c r="F62" s="3">
         <v>954000</v>
       </c>
-      <c r="F62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="G62" s="3" t="s">
         <v>8</v>
       </c>
       <c r="H62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I62" s="3">
+      <c r="I62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J62" s="3">
         <v>257000</v>
       </c>
-      <c r="J62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K62" s="3" t="s">
         <v>8</v>
       </c>
       <c r="L62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M62" s="3">
+      <c r="M62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N62" s="3">
         <v>366000</v>
       </c>
-      <c r="N62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O62" s="3">
+      <c r="O62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P62" s="3">
         <v>44000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>5000</v>
       </c>
-      <c r="Q62" s="3">
-        <v>0</v>
-      </c>
       <c r="R62" s="3">
         <v>0</v>
       </c>
       <c r="S62" s="3">
+        <v>0</v>
+      </c>
+      <c r="T62" s="3">
         <v>831000</v>
       </c>
-      <c r="T62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U62" s="3" t="s">
         <v>8</v>
       </c>
@@ -6682,62 +6828,65 @@
       <c r="X62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Y62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z62" s="3">
         <v>18272000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>15817000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>14520000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>14479000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>16539000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>15298000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>16077000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>14783000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>13048000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>12335000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>12605000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>11714000</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>12833000</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>13237000</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>12651000</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>9882000</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>9767000</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>11450000</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6858,8 +7007,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6980,8 +7132,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7102,62 +7257,65 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>8212000</v>
+      </c>
+      <c r="E66" s="3">
         <v>6702000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>6737000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>5847000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>5113000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>4073000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2966000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>3098000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2945000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2652000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2825000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2695000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>934000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>973000</v>
       </c>
-      <c r="Q66" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R66" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S66" s="3">
+      <c r="S66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T66" s="3">
         <v>19657000</v>
       </c>
-      <c r="T66" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U66" s="3" t="s">
         <v>8</v>
       </c>
@@ -7170,62 +7328,65 @@
       <c r="X66" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Y66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z66" s="3">
         <v>307858000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>293932000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>284365000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>279773000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>288956000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>257836000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>255531000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>233682000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>226466000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>207078000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>170595000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>167287000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>164476000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>157417000</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>151905000</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>139535000</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>133373000</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>133673000</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7268,8 +7429,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7390,8 +7552,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7512,8 +7677,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7581,7 +7749,7 @@
         <v>0</v>
       </c>
       <c r="Y70" s="3">
-        <v>4145000</v>
+        <v>0</v>
       </c>
       <c r="Z70" s="3">
         <v>4145000</v>
@@ -7599,16 +7767,16 @@
         <v>4145000</v>
       </c>
       <c r="AE70" s="3">
+        <v>4145000</v>
+      </c>
+      <c r="AF70" s="3">
         <v>4146000</v>
       </c>
-      <c r="AF70" s="3">
+      <c r="AG70" s="3">
         <v>4149000</v>
       </c>
-      <c r="AG70" s="3">
+      <c r="AH70" s="3">
         <v>4168000</v>
-      </c>
-      <c r="AH70" s="3">
-        <v>4192000</v>
       </c>
       <c r="AI70" s="3">
         <v>4192000</v>
@@ -7620,22 +7788,25 @@
         <v>4192000</v>
       </c>
       <c r="AL70" s="3">
+        <v>4192000</v>
+      </c>
+      <c r="AM70" s="3">
         <v>4196000</v>
       </c>
-      <c r="AM70" s="3">
+      <c r="AN70" s="3">
         <v>3949000</v>
       </c>
-      <c r="AN70" s="3">
+      <c r="AO70" s="3">
         <v>3950000</v>
       </c>
-      <c r="AO70" s="3">
+      <c r="AP70" s="3">
         <v>3954000</v>
       </c>
-      <c r="AP70" s="3">
+      <c r="AQ70" s="3">
         <v>3732000</v>
       </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7756,62 +7927,65 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-950000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1047000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-851000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-704000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-715000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-617000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-488000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-553000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-481000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-362000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-178000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-27000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-1000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>17000</v>
       </c>
-      <c r="Q72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S72" s="3">
+      <c r="S72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T72" s="3">
         <v>7716000</v>
       </c>
-      <c r="T72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U72" s="3" t="s">
         <v>8</v>
       </c>
@@ -7824,62 +7998,65 @@
       <c r="X72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Y72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z72" s="3">
         <v>15952000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>15208000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>14911000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>15567000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>16408000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>15868000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>15205000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>15076000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>14551000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>13042000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>13016000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>12439000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>11899000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>11137000</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>10997000</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>10973000</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>11182000</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>10827000</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -8000,8 +8177,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8122,8 +8302,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8244,62 +8427,65 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>7513000</v>
+      </c>
+      <c r="E76" s="3">
         <v>7592000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>8118000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>8461000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>8470000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>8489000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>8752000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>8708000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>8733000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>8796000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>9126000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>9213000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2225000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>2320000</v>
       </c>
-      <c r="Q76" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R76" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S76" s="3">
+      <c r="S76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T76" s="3">
         <v>7862000</v>
       </c>
-      <c r="T76" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U76" s="3" t="s">
         <v>8</v>
       </c>
@@ -8312,62 +8498,65 @@
       <c r="X76" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Y76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z76" s="3">
         <v>31693000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>29006000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>27925000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>28665000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>30868000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>29427000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>26659000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>26394000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>25647000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>22691000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>24381000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>24456000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>24052000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>22964000</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>22329000</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>22511000</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>22499000</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>22432000</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8488,257 +8677,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2" t="s">
-        <v>8</v>
-      </c>
       <c r="R80" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="S80" s="2">
+      <c r="S80" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="X80" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y80" s="2">
+      <c r="Y80" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>904000</v>
+      </c>
+      <c r="E81" s="3">
         <v>617000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>560000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>724000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>620000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>581000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>688000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>544000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>495000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>441000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>374000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>494000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>109000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>125000</v>
       </c>
-      <c r="Q81" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R81" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S81" s="3">
+      <c r="S81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T81" s="3">
         <v>668000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>348000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>1869000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>414000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>427000</v>
       </c>
-      <c r="X81" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y81" s="3">
+      <c r="Y81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z81" s="3">
         <v>607000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>138000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-692000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-328000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>807000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>909000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>361000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>578000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>1847000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>125000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>642000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>819000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>1007000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>193000</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>190000</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>-73000</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>140000</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>1003000</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8781,37 +8979,38 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>3000</v>
+        <v>11000</v>
       </c>
       <c r="E83" s="3">
         <v>3000</v>
       </c>
       <c r="F83" s="3">
+        <v>3000</v>
+      </c>
+      <c r="G83" s="3">
         <v>4000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>3000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>4000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>1000</v>
-      </c>
-      <c r="J83" s="3">
-        <v>3000</v>
       </c>
       <c r="K83" s="3">
         <v>3000</v>
       </c>
       <c r="L83" s="3">
-        <v>4000</v>
+        <v>3000</v>
       </c>
       <c r="M83" s="3">
         <v>4000</v>
@@ -8819,92 +9018,95 @@
       <c r="N83" s="3">
         <v>4000</v>
       </c>
-      <c r="O83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P83" s="3">
+      <c r="O83" s="3">
+        <v>4000</v>
+      </c>
+      <c r="P83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q83" s="3">
         <v>3000</v>
       </c>
-      <c r="Q83" s="3">
-        <v>0</v>
-      </c>
       <c r="R83" s="3">
         <v>0</v>
       </c>
       <c r="S83" s="3">
+        <v>0</v>
+      </c>
+      <c r="T83" s="3">
         <v>2000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>3000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>11000</v>
-      </c>
-      <c r="V83" s="3">
-        <v>2000</v>
       </c>
       <c r="W83" s="3">
         <v>2000</v>
       </c>
-      <c r="X83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y83" s="3">
+      <c r="X83" s="3">
+        <v>2000</v>
+      </c>
+      <c r="Y83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z83" s="3">
         <v>1536000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>1470000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>1376000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>1409000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>1309000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>1299000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>1234000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>1034000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>927000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>833000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>672000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>670000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>590000</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>643000</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>613000</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>499000</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>482000</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>541000</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9025,8 +9227,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9147,8 +9352,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9269,8 +9477,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9391,8 +9602,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9513,130 +9727,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>545000</v>
+      </c>
+      <c r="E89" s="3">
         <v>338000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>706000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>745000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>529000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>114000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>136000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>567000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>393000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>516000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>345000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>599000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>134000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>133000</v>
       </c>
-      <c r="Q89" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R89" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S89" s="3">
+      <c r="S89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T89" s="3">
         <v>2667000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-399000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1443000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>2040000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-632000</v>
       </c>
-      <c r="X89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y89" s="3">
+      <c r="Y89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z89" s="3">
         <v>2843000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>2202000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>1613000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>1706000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>2046000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>1898000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>837000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1540000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>2509000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>483000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>911000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>1255000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>1178000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>1109000</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>1159000</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>539000</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>1364000</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>635000</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9679,130 +9899,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-10000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-6000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-2000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-4000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-2000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-3000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-2000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-124000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-3000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-4000</v>
       </c>
-      <c r="N91" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P91" s="3">
+      <c r="P91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-41000</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
       <c r="R91" s="3">
         <v>0</v>
       </c>
       <c r="S91" s="3">
+        <v>0</v>
+      </c>
+      <c r="T91" s="3">
         <v>-2000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-17000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-35000</v>
       </c>
-      <c r="V91" s="3">
-        <v>0</v>
-      </c>
-      <c r="W91" s="3" t="s">
-        <v>8</v>
+      <c r="W91" s="3">
+        <v>0</v>
       </c>
       <c r="X91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Y91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z91" s="3">
         <v>-1138000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-882000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-1117000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-875000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-1080000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-783000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-652000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-538000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-697000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-516000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-398000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-351000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-462000</v>
-      </c>
-      <c r="AL91" s="3">
-        <v>-419000</v>
       </c>
       <c r="AM91" s="3">
         <v>-419000</v>
       </c>
       <c r="AN91" s="3">
+        <v>-419000</v>
+      </c>
+      <c r="AO91" s="3">
         <v>-787000</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-1015000</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-668000</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9923,8 +10147,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10045,130 +10272,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-308000</v>
+      </c>
+      <c r="E94" s="3">
         <v>160000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-76000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-8000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-490000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>235000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>37000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1323000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-452000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-6000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-266000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>36000</v>
       </c>
-      <c r="O94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P94" s="3">
+      <c r="P94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q94" s="3">
         <v>-41000</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S94" s="3">
+      <c r="S94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T94" s="3">
         <v>-339000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>262000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-861000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>385000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-356000</v>
       </c>
-      <c r="X94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y94" s="3">
+      <c r="Y94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z94" s="3">
         <v>-1121000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-7000000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-3665000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-2087000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-12918000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-3777000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-16748000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-3231000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-9907000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-4851000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-3677000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-1398000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-784000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-2391000</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-6894000</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-1325000</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-2497000</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-182000</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10211,52 +10444,53 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>802000</v>
+      </c>
+      <c r="E96" s="3">
         <v>809000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>703000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>706000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>702000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>707000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>619000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>620000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>619000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>620000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>525000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>524000</v>
-      </c>
-      <c r="O96" s="3">
-        <v>127000</v>
       </c>
       <c r="P96" s="3">
         <v>127000</v>
       </c>
       <c r="Q96" s="3">
-        <v>0</v>
+        <v>127000</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -10280,61 +10514,64 @@
         <v>0</v>
       </c>
       <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-217000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-216000</v>
-      </c>
-      <c r="AA96" s="3">
-        <v>-217000</v>
       </c>
       <c r="AB96" s="3">
         <v>-217000</v>
       </c>
       <c r="AC96" s="3">
+        <v>-217000</v>
+      </c>
+      <c r="AD96" s="3">
         <v>-200000</v>
-      </c>
-      <c r="AD96" s="3">
-        <v>-191000</v>
       </c>
       <c r="AE96" s="3">
         <v>-191000</v>
       </c>
       <c r="AF96" s="3">
+        <v>-191000</v>
+      </c>
+      <c r="AG96" s="3">
         <v>-190000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-181000</v>
-      </c>
-      <c r="AH96" s="3">
-        <v>-182000</v>
       </c>
       <c r="AI96" s="3">
         <v>-182000</v>
       </c>
       <c r="AJ96" s="3">
+        <v>-182000</v>
+      </c>
+      <c r="AK96" s="3">
         <v>-181000</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-149000</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-195000</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
         <v>-170000</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-171000</v>
-      </c>
-      <c r="AO96" s="3">
-        <v>-158000</v>
       </c>
       <c r="AP96" s="3">
         <v>-158000</v>
       </c>
+      <c r="AQ96" s="3">
+        <v>-158000</v>
+      </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10455,8 +10692,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10577,8 +10817,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10699,130 +10942,136 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>173000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-983000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-108000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-161000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>108000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-422000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-659000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-277000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-603000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-580000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-357000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-608000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-134000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-81000</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S100" s="3">
+      <c r="S100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T100" s="3">
         <v>-2265000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>222000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-187000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-2165000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>1072000</v>
       </c>
-      <c r="X100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y100" s="3">
+      <c r="Y100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z100" s="3">
         <v>-706000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>3940000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>1627000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>3837000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>9973000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>2166000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>16582000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>25000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>7957000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>6353000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>2784000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>1042000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>211000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>1360000</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>3756000</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>2858000</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>1137000</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>-119000</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10830,20 +11079,20 @@
         <v>1000</v>
       </c>
       <c r="E101" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F101" s="3">
         <v>-13000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>5000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-1000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-3000</v>
       </c>
-      <c r="I101" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J101" s="3" t="s">
         <v>8</v>
       </c>
@@ -10853,21 +11102,21 @@
       <c r="L101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M101" s="3">
+      <c r="M101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N101" s="3">
         <v>2000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-1000</v>
       </c>
-      <c r="O101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P101" s="3">
+      <c r="P101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q101" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
-      </c>
       <c r="R101" s="3">
         <v>0</v>
       </c>
@@ -10875,194 +11124,200 @@
         <v>0</v>
       </c>
       <c r="T101" s="3">
-        <v>-2000</v>
+        <v>0</v>
       </c>
       <c r="U101" s="3">
         <v>-2000</v>
       </c>
       <c r="V101" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="W101" s="3">
         <v>1000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-2000</v>
       </c>
-      <c r="X101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y101" s="3">
+      <c r="Y101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z101" s="3">
         <v>194000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>58000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>80000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-366000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>82000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-139000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>36000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>16000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-8000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-59000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-149000</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>6000</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>-4000</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>31000</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>-19000</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>56000</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>-77000</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>18000</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>407000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-487000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>521000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>582000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>148000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-72000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-499000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-1028000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-663000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-73000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-278000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>27000</v>
       </c>
-      <c r="O102" s="3">
-        <v>0</v>
-      </c>
       <c r="P102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q102" s="3">
         <v>11000</v>
       </c>
-      <c r="Q102" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R102" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S102" s="3">
+      <c r="S102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T102" s="3">
         <v>63000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>83000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>393000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>261000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>82000</v>
       </c>
-      <c r="X102" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y102" s="3">
+      <c r="Y102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z102" s="3">
         <v>1210000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-800000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-345000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>3090000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-817000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>148000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>707000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-1650000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>551000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>1926000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-131000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>905000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>601000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>109000</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-1998000</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>2128000</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>-73000</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>352000</v>
       </c>
     </row>
